--- a/HRManagementAPI/uploads/HR Database Dummy Data.xlsx
+++ b/HRManagementAPI/uploads/HR Database Dummy Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simbe\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simbe\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF16D91F-2EE9-4ADB-9394-37FA71514811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF86429B-0AA2-43D1-BB45-E6EC76B742C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D637D0AC-18DE-4DD5-9F55-DFCA20DCFFAF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>Last Name</t>
   </si>
@@ -92,15 +92,6 @@
     <t>&lt;25</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>Field Staff</t>
-  </si>
-  <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>Family Model Provider</t>
   </si>
   <si>
@@ -140,21 +131,6 @@
     <t>Nursing License Expiration</t>
   </si>
   <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>Hall</t>
-  </si>
-  <si>
-    <t>Mathis</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Rachel</t>
-  </si>
-  <si>
     <t>Valerie</t>
   </si>
   <si>
@@ -189,6 +165,24 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>jkkk</t>
+  </si>
+  <si>
+    <t>gyyy</t>
+  </si>
+  <si>
+    <t>ffgg</t>
+  </si>
+  <si>
+    <t>cdfdf</t>
+  </si>
+  <si>
+    <t>Finance</t>
   </si>
 </sst>
 </file>
@@ -653,7 +647,7 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J1" t="s">
         <v>7</v>
@@ -668,21 +662,21 @@
         <v>10</v>
       </c>
       <c r="N1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
         <v>43522</v>
@@ -691,13 +685,13 @@
         <v>20605</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
@@ -706,22 +700,22 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="O2" s="2">
-        <v>46018</v>
+        <v>46383</v>
       </c>
       <c r="P2" s="2">
         <v>46054</v>
@@ -729,10 +723,10 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2">
         <v>40178</v>
@@ -741,13 +735,13 @@
         <v>37009</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
@@ -756,30 +750,33 @@
         <v>16</v>
       </c>
       <c r="J3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" t="s">
         <v>25</v>
       </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O3" s="2">
         <v>46809</v>
       </c>
+      <c r="P3" s="2">
+        <v>45753</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2">
         <v>45843</v>
@@ -788,13 +785,13 @@
         <v>28666</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -803,22 +800,25 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" t="s">
         <v>26</v>
       </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="O4" s="2">
         <v>46053</v>
+      </c>
+      <c r="P4" s="2">
+        <v>46045</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
